--- a/testData/APIInfo.xlsx
+++ b/testData/APIInfo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tianxiang1\pythonProject\testData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\review\pythonproject\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D36A95D-FAE5-4D2C-AB99-BD8F10148554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67D5944-A2DF-47D0-83E8-399AF93661FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19460" windowHeight="10910" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="asserts" sheetId="34" r:id="rId1"/>
@@ -1147,19 +1147,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9980EC5-3269-415C-BBB0-0DE30C121511}">
   <dimension ref="A1:K52"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.5" customWidth="1"/>
-    <col min="2" max="2" width="42.5" style="11" customWidth="1"/>
-    <col min="3" max="3" width="42.5" customWidth="1"/>
-    <col min="4" max="4" width="105.75" customWidth="1"/>
-    <col min="5" max="5" width="102.5" customWidth="1"/>
-    <col min="7" max="8" width="25.375" customWidth="1"/>
-    <col min="9" max="10" width="29.625" customWidth="1"/>
-    <col min="11" max="11" width="5.375" customWidth="1"/>
+    <col min="1" max="1" width="27.453125" customWidth="1"/>
+    <col min="2" max="2" width="42.453125" style="11" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" customWidth="1"/>
+    <col min="4" max="4" width="105.7265625" customWidth="1"/>
+    <col min="5" max="5" width="102.453125" customWidth="1"/>
+    <col min="7" max="8" width="25.36328125" customWidth="1"/>
+    <col min="9" max="10" width="29.6328125" customWidth="1"/>
+    <col min="11" max="11" width="5.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1194,7 +1194,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
@@ -1225,7 +1225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>72</v>
       </c>
@@ -1253,7 +1253,7 @@
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>21</v>
       </c>
@@ -1281,7 +1281,7 @@
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
     </row>
-    <row r="5" spans="1:11" ht="81" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:11" ht="84" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>29</v>
       </c>
@@ -1313,7 +1313,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>30</v>
       </c>
@@ -1341,7 +1341,7 @@
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>39</v>
       </c>
@@ -1369,7 +1369,7 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>44</v>
       </c>
@@ -1397,7 +1397,7 @@
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>52</v>
       </c>
@@ -1423,7 +1423,7 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>55</v>
       </c>
@@ -1451,7 +1451,7 @@
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
     </row>
-    <row r="11" spans="1:11" ht="27" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:11" ht="28" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>59</v>
       </c>
@@ -1479,7 +1479,7 @@
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>60</v>
       </c>
@@ -1511,7 +1511,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>64</v>
       </c>
@@ -1539,7 +1539,7 @@
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>67</v>
       </c>
@@ -1567,7 +1567,7 @@
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" spans="1:11" ht="27" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:11" ht="28" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>80</v>
       </c>
@@ -1595,7 +1595,7 @@
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="2"/>
@@ -1607,7 +1607,7 @@
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="2"/>
@@ -1619,7 +1619,7 @@
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="2"/>
@@ -1631,7 +1631,7 @@
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="2"/>
@@ -1643,7 +1643,7 @@
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="2"/>
@@ -1655,7 +1655,7 @@
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="2"/>
@@ -1667,7 +1667,7 @@
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="2"/>
@@ -1679,7 +1679,7 @@
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="2"/>
@@ -1691,7 +1691,7 @@
       <c r="I23" s="6"/>
       <c r="J23" s="6"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="2"/>
@@ -1703,7 +1703,7 @@
       <c r="I24" s="6"/>
       <c r="J24" s="6"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="2"/>
@@ -1715,7 +1715,7 @@
       <c r="I25" s="6"/>
       <c r="J25" s="6"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="2"/>
@@ -1727,7 +1727,7 @@
       <c r="I26" s="6"/>
       <c r="J26" s="6"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="2"/>
@@ -1739,7 +1739,7 @@
       <c r="I27" s="6"/>
       <c r="J27" s="6"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="2"/>
@@ -1751,7 +1751,7 @@
       <c r="I28" s="6"/>
       <c r="J28" s="6"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="2"/>
@@ -1763,7 +1763,7 @@
       <c r="I29" s="6"/>
       <c r="J29" s="6"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="2"/>
@@ -1775,7 +1775,7 @@
       <c r="I30" s="6"/>
       <c r="J30" s="6"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="2"/>
@@ -1787,7 +1787,7 @@
       <c r="I31" s="6"/>
       <c r="J31" s="6"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="2"/>
@@ -1799,7 +1799,7 @@
       <c r="I32" s="6"/>
       <c r="J32" s="6"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="2"/>
@@ -1811,7 +1811,7 @@
       <c r="I33" s="6"/>
       <c r="J33" s="6"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="2"/>
@@ -1823,7 +1823,7 @@
       <c r="I34" s="6"/>
       <c r="J34" s="6"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="2"/>
@@ -1835,7 +1835,7 @@
       <c r="I35" s="6"/>
       <c r="J35" s="6"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="2"/>
@@ -1847,7 +1847,7 @@
       <c r="I36" s="6"/>
       <c r="J36" s="6"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="2"/>
@@ -1859,7 +1859,7 @@
       <c r="I37" s="6"/>
       <c r="J37" s="6"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="2"/>
@@ -1871,7 +1871,7 @@
       <c r="I38" s="6"/>
       <c r="J38" s="6"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="2"/>
@@ -1883,7 +1883,7 @@
       <c r="I39" s="6"/>
       <c r="J39" s="6"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="2"/>
@@ -1895,7 +1895,7 @@
       <c r="I40" s="6"/>
       <c r="J40" s="6"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="2"/>
@@ -1907,7 +1907,7 @@
       <c r="I41" s="6"/>
       <c r="J41" s="6"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="2"/>
@@ -1919,7 +1919,7 @@
       <c r="I42" s="6"/>
       <c r="J42" s="6"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="2"/>
@@ -1931,7 +1931,7 @@
       <c r="I43" s="6"/>
       <c r="J43" s="6"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="2"/>
@@ -1943,7 +1943,7 @@
       <c r="I44" s="6"/>
       <c r="J44" s="6"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="2"/>
@@ -1955,7 +1955,7 @@
       <c r="I45" s="6"/>
       <c r="J45" s="6"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="2"/>
@@ -1967,7 +1967,7 @@
       <c r="I46" s="6"/>
       <c r="J46" s="6"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="2"/>
@@ -1979,7 +1979,7 @@
       <c r="I47" s="6"/>
       <c r="J47" s="6"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="2"/>
@@ -1991,7 +1991,7 @@
       <c r="I48" s="6"/>
       <c r="J48" s="6"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="2"/>
@@ -2004,7 +2004,7 @@
       <c r="J49" s="6"/>
       <c r="K49" s="2"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="2"/>
@@ -2017,7 +2017,7 @@
       <c r="J50" s="7"/>
       <c r="K50" s="8"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="2"/>
@@ -2028,7 +2028,7 @@
       <c r="H51" s="8"/>
       <c r="K51" s="8"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="2"/>
@@ -2050,19 +2050,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DD3B8D0-DBB5-4D0A-9099-35E53693938E}">
   <dimension ref="A1:K52"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.5" customWidth="1"/>
-    <col min="2" max="2" width="42.5" style="11" customWidth="1"/>
-    <col min="3" max="3" width="42.5" customWidth="1"/>
-    <col min="4" max="4" width="84.75" customWidth="1"/>
-    <col min="5" max="5" width="102.5" customWidth="1"/>
-    <col min="7" max="8" width="25.375" customWidth="1"/>
-    <col min="9" max="10" width="29.625" customWidth="1"/>
-    <col min="11" max="11" width="5.375" customWidth="1"/>
+    <col min="1" max="1" width="27.453125" customWidth="1"/>
+    <col min="2" max="2" width="42.453125" style="11" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" customWidth="1"/>
+    <col min="4" max="4" width="84.7265625" customWidth="1"/>
+    <col min="5" max="5" width="102.453125" customWidth="1"/>
+    <col min="7" max="8" width="25.36328125" customWidth="1"/>
+    <col min="9" max="10" width="29.6328125" customWidth="1"/>
+    <col min="11" max="11" width="5.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2097,7 +2097,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="2" customFormat="1" ht="409.5" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:11" s="2" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
@@ -2125,7 +2125,7 @@
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
     </row>
-    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="E3" s="5"/>
@@ -2135,7 +2135,7 @@
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="2"/>
@@ -2147,7 +2147,7 @@
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="2"/>
@@ -2159,7 +2159,7 @@
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="2"/>
@@ -2171,7 +2171,7 @@
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="2"/>
@@ -2183,7 +2183,7 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="2"/>
@@ -2195,7 +2195,7 @@
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="2"/>
@@ -2207,7 +2207,7 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="2"/>
@@ -2219,7 +2219,7 @@
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="2"/>
@@ -2231,7 +2231,7 @@
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="2"/>
@@ -2243,7 +2243,7 @@
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="2"/>
@@ -2255,7 +2255,7 @@
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="2"/>
@@ -2267,7 +2267,7 @@
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="2"/>
@@ -2279,7 +2279,7 @@
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="2"/>
@@ -2291,7 +2291,7 @@
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="2"/>
@@ -2303,7 +2303,7 @@
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="2"/>
@@ -2315,7 +2315,7 @@
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="2"/>
@@ -2327,7 +2327,7 @@
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="2"/>
@@ -2339,7 +2339,7 @@
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="2"/>
@@ -2351,7 +2351,7 @@
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="2"/>
@@ -2363,7 +2363,7 @@
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="2"/>
@@ -2375,7 +2375,7 @@
       <c r="I23" s="6"/>
       <c r="J23" s="6"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="2"/>
@@ -2387,7 +2387,7 @@
       <c r="I24" s="6"/>
       <c r="J24" s="6"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="2"/>
@@ -2399,7 +2399,7 @@
       <c r="I25" s="6"/>
       <c r="J25" s="6"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="2"/>
@@ -2411,7 +2411,7 @@
       <c r="I26" s="6"/>
       <c r="J26" s="6"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="2"/>
@@ -2423,7 +2423,7 @@
       <c r="I27" s="6"/>
       <c r="J27" s="6"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="2"/>
@@ -2435,7 +2435,7 @@
       <c r="I28" s="6"/>
       <c r="J28" s="6"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="2"/>
@@ -2447,7 +2447,7 @@
       <c r="I29" s="6"/>
       <c r="J29" s="6"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="2"/>
@@ -2459,7 +2459,7 @@
       <c r="I30" s="6"/>
       <c r="J30" s="6"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="2"/>
@@ -2471,7 +2471,7 @@
       <c r="I31" s="6"/>
       <c r="J31" s="6"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="2"/>
@@ -2483,7 +2483,7 @@
       <c r="I32" s="6"/>
       <c r="J32" s="6"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="2"/>
@@ -2495,7 +2495,7 @@
       <c r="I33" s="6"/>
       <c r="J33" s="6"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="2"/>
@@ -2507,7 +2507,7 @@
       <c r="I34" s="6"/>
       <c r="J34" s="6"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="2"/>
@@ -2519,7 +2519,7 @@
       <c r="I35" s="6"/>
       <c r="J35" s="6"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="2"/>
@@ -2531,7 +2531,7 @@
       <c r="I36" s="6"/>
       <c r="J36" s="6"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="2"/>
@@ -2543,7 +2543,7 @@
       <c r="I37" s="6"/>
       <c r="J37" s="6"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="2"/>
@@ -2555,7 +2555,7 @@
       <c r="I38" s="6"/>
       <c r="J38" s="6"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="2"/>
@@ -2567,7 +2567,7 @@
       <c r="I39" s="6"/>
       <c r="J39" s="6"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="2"/>
@@ -2579,7 +2579,7 @@
       <c r="I40" s="6"/>
       <c r="J40" s="6"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="2"/>
@@ -2591,7 +2591,7 @@
       <c r="I41" s="6"/>
       <c r="J41" s="6"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="2"/>
@@ -2603,7 +2603,7 @@
       <c r="I42" s="6"/>
       <c r="J42" s="6"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="2"/>
@@ -2615,7 +2615,7 @@
       <c r="I43" s="6"/>
       <c r="J43" s="6"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="2"/>
@@ -2627,7 +2627,7 @@
       <c r="I44" s="6"/>
       <c r="J44" s="6"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="2"/>
@@ -2639,7 +2639,7 @@
       <c r="I45" s="6"/>
       <c r="J45" s="6"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="2"/>
@@ -2651,7 +2651,7 @@
       <c r="I46" s="6"/>
       <c r="J46" s="6"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="2"/>
@@ -2663,7 +2663,7 @@
       <c r="I47" s="6"/>
       <c r="J47" s="6"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="2"/>
@@ -2675,7 +2675,7 @@
       <c r="I48" s="6"/>
       <c r="J48" s="6"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="2"/>
@@ -2688,7 +2688,7 @@
       <c r="J49" s="6"/>
       <c r="K49" s="2"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="2"/>
@@ -2701,7 +2701,7 @@
       <c r="J50" s="7"/>
       <c r="K50" s="8"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="2"/>
@@ -2712,7 +2712,7 @@
       <c r="H51" s="8"/>
       <c r="K51" s="8"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="2"/>
